--- a/Excel/ItemConfig@cs.xlsx
+++ b/Excel/ItemConfig@cs.xlsx
@@ -69,7 +69,7 @@
     <t>最大累加数量</t>
   </si>
   <si>
-    <t>s词条随机Id</t>
+    <t>s词条随机表中的Id</t>
   </si>
   <si>
     <t>售卖的基础价格</t>
@@ -1214,7 +1214,8 @@
     <col min="5" max="5" width="39.625" style="1" customWidth="1"/>
     <col min="6" max="7" width="11" style="1" customWidth="1"/>
     <col min="8" max="9" width="14.375" style="1" customWidth="1"/>
-    <col min="10" max="11" width="12.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.225" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
